--- a/data/trans_dic/IMC_inf_MED_R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R3-Estudios-trans_dic.xlsx
@@ -532,7 +532,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 71,23%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,31 +632,31 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.2697868897876032</v>
+        <v>0.2453516141026484</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.2367804882764704</v>
+        <v>0.2050432413659233</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>0.1797067672596934</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.2160504150119885</v>
+        <v>0.1928872995419658</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.2290134171815054</v>
+        <v>0.1831492391143975</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.09736959081109881</v>
+        <v>0.1562371040635662</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.240948064241383</v>
+        <v>0.2183144195009455</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.2333641861740443</v>
+        <v>0.1954147610513214</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0.14643087905149</v>
+        <v>0.1693778778595711</v>
       </c>
     </row>
     <row r="5">
@@ -667,31 +667,31 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.1843338404266488</v>
+        <v>0.1728613541226593</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.1471836650798361</v>
+        <v>0.1356495079894939</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0.0721901388400441</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.1443470013638928</v>
+        <v>0.1289971553595373</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.1339722316586565</v>
+        <v>0.1052743513897078</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.02369520949375807</v>
+        <v>0.05783610223089332</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.1831767518522177</v>
+        <v>0.1672593484848563</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.1627691202218707</v>
+        <v>0.1405445706352267</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.071133721668448</v>
+        <v>0.08968601638465248</v>
       </c>
     </row>
     <row r="6">
@@ -702,31 +702,31 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.3760243059318696</v>
+        <v>0.3312314717598057</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.3411054913717556</v>
+        <v>0.2946623384939361</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0.3524162045190609</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.3027629826629089</v>
+        <v>0.2708125958389401</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.3707514198883032</v>
+        <v>0.2788323867863247</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.2920423664243431</v>
+        <v>0.3338652948220358</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.3122810185984908</v>
+        <v>0.2795625211934821</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.3104003281570981</v>
+        <v>0.266915908774556</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>0.2647422697182116</v>
+        <v>0.2944651159708576</v>
       </c>
     </row>
     <row r="7">
@@ -741,31 +741,31 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.2967162975150009</v>
+        <v>0.2748833697364035</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.2297374652403917</v>
+        <v>0.225888631344264</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.2355112849878541</v>
+        <v>0.2263733428791819</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.2290067899593227</v>
+        <v>0.2246824811421367</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.1281733092405487</v>
+        <v>0.1176853673456414</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.1304361257414428</v>
+        <v>0.1268238634202751</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.264381751062037</v>
+        <v>0.2508786405871642</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.1803686956288567</v>
+        <v>0.1737595116426006</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.1903138920268281</v>
+        <v>0.1834491179392568</v>
       </c>
     </row>
     <row r="8">
@@ -776,31 +776,31 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.2572349030892979</v>
+        <v>0.2387972576418479</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.1948617247385736</v>
+        <v>0.1934149216394691</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.1881770814806643</v>
+        <v>0.1778179003016295</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.1949043245057975</v>
+        <v>0.189353959494261</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.100929923861058</v>
+        <v>0.09442139040811647</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.08825369640195196</v>
+        <v>0.09205922268498874</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.2380426157967588</v>
+        <v>0.2268073980453173</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.1585172348167566</v>
+        <v>0.1537993078524299</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.1555936040916557</v>
+        <v>0.1496419685188169</v>
       </c>
     </row>
     <row r="9">
@@ -811,31 +811,31 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.341068908620047</v>
+        <v>0.3118328254337757</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.2663825861743778</v>
+        <v>0.2619384822641451</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.293989180434569</v>
+        <v>0.2785677453680547</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.2695837248274655</v>
+        <v>0.2610154143959589</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.1604881522893255</v>
+        <v>0.1481244192088572</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.1782563693784863</v>
+        <v>0.178775272003855</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.2953679838676471</v>
+        <v>0.2805916244082707</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.2028377877151161</v>
+        <v>0.1976232286989918</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.2260570932711554</v>
+        <v>0.2227263851064879</v>
       </c>
     </row>
     <row r="10">
@@ -850,31 +850,31 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.2409044225629987</v>
+        <v>0.2181792186523086</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.1607892148553552</v>
+        <v>0.1354240490576121</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.1043843109024222</v>
+        <v>0.09810466541518707</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.1900588478793153</v>
+        <v>0.1810806414793902</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.1414506697024728</v>
+        <v>0.1377097425669956</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.0927567874098985</v>
+        <v>0.0907735430490304</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.2156043471214577</v>
+        <v>0.1995925757920209</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.151421643783798</v>
+        <v>0.1365247886278317</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.09867952959703892</v>
+        <v>0.09458185390574632</v>
       </c>
     </row>
     <row r="11">
@@ -885,31 +885,31 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.1779772052707136</v>
+        <v>0.1615254975785956</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.1141798401160793</v>
+        <v>0.09233139325303784</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.05504021530988456</v>
+        <v>0.05458049924489888</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.132182226997245</v>
+        <v>0.1257451191098143</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.09631290075288165</v>
+        <v>0.09456756391151505</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.04863096359135285</v>
+        <v>0.04529581373058516</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.1760200720398474</v>
+        <v>0.1622817861940415</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.1142533111999823</v>
+        <v>0.1087634343135501</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.0614771900672899</v>
+        <v>0.0597630388748083</v>
       </c>
     </row>
     <row r="12">
@@ -920,31 +920,31 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.3093407452875923</v>
+        <v>0.2783018572324175</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.2296252850385614</v>
+        <v>0.18267893125157</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.1754158152695646</v>
+        <v>0.172512167990137</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.252148140810452</v>
+        <v>0.243073145192523</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.2059235416234743</v>
+        <v>0.1900422851931999</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.1609308347912576</v>
+        <v>0.1568210945320703</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.2616136504836925</v>
+        <v>0.2448459612357383</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.192818539617634</v>
+        <v>0.1796919047155046</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.1431629582184692</v>
+        <v>0.1395021029281398</v>
       </c>
     </row>
     <row r="13">
@@ -959,31 +959,31 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.2810594781674127</v>
+        <v>0.2587597419028065</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.2147325958129284</v>
+        <v>0.2026631501550434</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.199577453218781</v>
+        <v>0.1916390354652999</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.218121588944378</v>
+        <v>0.2102289689071407</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.1391908963230728</v>
+        <v>0.128250271495198</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.1172497653739078</v>
+        <v>0.1190293316454167</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.2502647366916653</v>
+        <v>0.2350712253584804</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.1783443098308589</v>
+        <v>0.167118795285524</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.1630330031050146</v>
+        <v>0.1593531132002171</v>
       </c>
     </row>
     <row r="14">
@@ -994,31 +994,31 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.2505511104084192</v>
+        <v>0.2314193338361696</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.1870940664698035</v>
+        <v>0.176747335080706</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.1610977255455545</v>
+        <v>0.1558067116395825</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.1890184602461841</v>
+        <v>0.1842705667851912</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.1175470932371663</v>
+        <v>0.10599752830818</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.08743334302902368</v>
+        <v>0.0884613013587426</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.2288614800298711</v>
+        <v>0.2156727653489396</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.159939460990371</v>
+        <v>0.1504129073899769</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.1388021358251922</v>
+        <v>0.1349931110562688</v>
       </c>
     </row>
     <row r="15">
@@ -1029,31 +1029,31 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.3133893808194827</v>
+        <v>0.2888995095664735</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.2481324942288383</v>
+        <v>0.2290646092616782</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.2475552608383892</v>
+        <v>0.2365777460481445</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.2487304796293391</v>
+        <v>0.2393603117884866</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.1691366455307075</v>
+        <v>0.1502560382600164</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.1571917747652832</v>
+        <v>0.1514604218648846</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.2734644421752407</v>
+        <v>0.2554472329920764</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.1994719594363856</v>
+        <v>0.1855186742623794</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.1903025231343647</v>
+        <v>0.1905684554140433</v>
       </c>
     </row>
     <row r="16">
@@ -1103,7 +1103,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 71,23%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1203,31 +1203,31 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>6</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -1238,31 +1238,31 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>15351</v>
+        <v>18591</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>11609</v>
+        <v>13431</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>4407</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>14239</v>
+        <v>15541</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>8817</v>
+        <v>9417</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1620</v>
+        <v>3012</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>29590</v>
+        <v>34132</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>20426</v>
+        <v>22848</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>6027</v>
+        <v>7419</v>
       </c>
     </row>
     <row r="6">
@@ -1273,31 +1273,31 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>10488</v>
+        <v>13098</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>7216</v>
+        <v>8885</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>1770</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>9513</v>
+        <v>10393</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>5158</v>
+        <v>5413</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>394</v>
+        <v>1115</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>22495</v>
+        <v>26150</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>14247</v>
+        <v>16433</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>2928</v>
+        <v>3928</v>
       </c>
     </row>
     <row r="7">
@@ -1308,31 +1308,31 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>21395</v>
+        <v>25098</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>16724</v>
+        <v>19301</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>8643</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>19954</v>
+        <v>21820</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>14274</v>
+        <v>14337</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>4858</v>
+        <v>6436</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>38350</v>
+        <v>43708</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>27169</v>
+        <v>31208</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>10896</v>
+        <v>12898</v>
       </c>
     </row>
     <row r="8">
@@ -1347,31 +1347,31 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>252</v>
+        <v>281</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9">
@@ -1382,31 +1382,31 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>102826</v>
+        <v>113014</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>81810</v>
+        <v>94639</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>47173</v>
+        <v>47628</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>72540</v>
+        <v>84647</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>43171</v>
+        <v>45837</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>19721</v>
+        <v>20227</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>175366</v>
+        <v>197661</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>124980</v>
+        <v>140476</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>66894</v>
+        <v>67855</v>
       </c>
     </row>
     <row r="10">
@@ -1417,31 +1417,31 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>89144</v>
+        <v>98178</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>69390</v>
+        <v>81034</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>37692</v>
+        <v>37412</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>61738</v>
+        <v>71337</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>33995</v>
+        <v>36776</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>13343</v>
+        <v>14682</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>157895</v>
+        <v>178696</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>109839</v>
+        <v>124339</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>54690</v>
+        <v>55350</v>
       </c>
     </row>
     <row r="11">
@@ -1452,31 +1452,31 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>118196</v>
+        <v>128205</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>94859</v>
+        <v>109743</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>58886</v>
+        <v>58610</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>85394</v>
+        <v>98335</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>54055</v>
+        <v>57693</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>26951</v>
+        <v>28513</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>195919</v>
+        <v>221071</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>140549</v>
+        <v>159768</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>79457</v>
+        <v>82383</v>
       </c>
     </row>
     <row r="12">
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>11</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>23</v>
@@ -1526,28 +1526,28 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>28703</v>
+        <v>30178</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>19149</v>
+        <v>19912</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>7358</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>22428</v>
+        <v>25148</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>15826</v>
+        <v>18809</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>6298</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>51131</v>
+        <v>55326</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>34975</v>
+        <v>38721</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>13656</v>
@@ -1561,31 +1561,31 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>21206</v>
+        <v>22342</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>13598</v>
+        <v>13576</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>3880</v>
+        <v>4094</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>15598</v>
+        <v>17463</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>10776</v>
+        <v>12917</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>3302</v>
+        <v>3143</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>41744</v>
+        <v>44984</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>26390</v>
+        <v>30848</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>8508</v>
+        <v>8629</v>
       </c>
     </row>
     <row r="15">
@@ -1596,31 +1596,31 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>36857</v>
+        <v>38494</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>27347</v>
+        <v>26860</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>12365</v>
+        <v>12939</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>29754</v>
+        <v>33757</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>23040</v>
+        <v>25957</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>10927</v>
+        <v>10880</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>62042</v>
+        <v>67870</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>44537</v>
+        <v>50964</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>19812</v>
+        <v>20142</v>
       </c>
     </row>
     <row r="16">
@@ -1635,31 +1635,31 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17">
@@ -1670,31 +1670,31 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>146880</v>
+        <v>161783</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>112567</v>
+        <v>127982</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>58938</v>
+        <v>59393</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>109207</v>
+        <v>125336</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>67814</v>
+        <v>74064</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>27638</v>
+        <v>29537</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>256087</v>
+        <v>287119</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>180381</v>
+        <v>202045</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>86577</v>
+        <v>88930</v>
       </c>
     </row>
     <row r="18">
@@ -1705,31 +1705,31 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>130936</v>
+        <v>144689</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>98079</v>
+        <v>111616</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>47575</v>
+        <v>48288</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>94636</v>
+        <v>109860</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>57269</v>
+        <v>61213</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>20610</v>
+        <v>21951</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>234185</v>
+        <v>263426</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>161766</v>
+        <v>181848</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>73709</v>
+        <v>75335</v>
       </c>
     </row>
     <row r="19">
@@ -1740,31 +1740,31 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>163775</v>
+        <v>180627</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>130076</v>
+        <v>144654</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>73107</v>
+        <v>73321</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>124532</v>
+        <v>142704</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>82403</v>
+        <v>86772</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>37054</v>
+        <v>37584</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>279826</v>
+        <v>312007</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>201750</v>
+        <v>224291</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>101058</v>
+        <v>106350</v>
       </c>
     </row>
     <row r="20">
